--- a/output/pdf_financials_xlsx/XBOT.xlsx
+++ b/output/pdf_financials_xlsx/XBOT.xlsx
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.904619</v>
+        <v>-1.904619</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3.758619</v>
+        <v>-3.758619</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>11.202989</v>
+        <v>-11.202989</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>15.113017</v>
+        <v>-15.113017</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>3.661177</v>
@@ -1146,13 +1146,13 @@
         </is>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.694438</v>
+        <v>-0.694438</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.585067</v>
+        <v>-0.585067</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.805903</v>
+        <v>-1.805903</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>-0.039686</v>
@@ -1183,10 +1183,10 @@
         <v>-0</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0.384943</v>
+        <v>-6.937411</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.080344</v>
       </c>
       <c r="H17" s="1" t="inlineStr">
         <is>
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.904619</v>
+        <v>-1.904619</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3.758619</v>
+        <v>-3.758619</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>11.202989</v>
+        <v>-11.202989</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>15.113017</v>
+        <v>-15.113017</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>3.276234</v>
+        <v>-3.276234</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1.040172</v>
+        <v>-1.040172</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1386,13 +1386,13 @@
         </is>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.694438</v>
+        <v>-0.694438</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.585067</v>
+        <v>-0.585067</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.805903</v>
+        <v>-1.805903</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>-0.039686</v>
@@ -1507,34 +1507,34 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>1.904619</v>
+        <v>-1.904619</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>3.758619</v>
+        <v>-3.758619</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>11.202989</v>
+        <v>-11.202989</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>15.113017</v>
+        <v>-15.113017</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>3.276234</v>
+        <v>-3.276234</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1.040172</v>
+        <v>-1.040172</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>5.375378</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.694438</v>
+        <v>-0.694438</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.585067</v>
+        <v>-0.585067</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.805903</v>
+        <v>-1.805903</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>-0.039686</v>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>112.02989</v>
+        <v>-112.02989</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>137.391064</v>
+        <v>-137.391064</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>163.8117</v>
+        <v>-163.8117</v>
       </c>
       <c r="G26" s="1" t="inlineStr">
         <is>
@@ -1751,16 +1751,16 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>1.904619</v>
+        <v>-1.904619</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>3.758619</v>
+        <v>-3.758619</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>11.202989</v>
+        <v>-11.202989</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>15.113017</v>
+        <v>-15.113017</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>3.661177</v>
@@ -1774,13 +1774,13 @@
         </is>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.694438</v>
+        <v>-0.694438</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.585067</v>
+        <v>-0.585067</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.805903</v>
+        <v>-1.805903</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>-0.039686</v>
@@ -1847,16 +1847,16 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>1.904619</v>
+        <v>-1.904619</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>3.758619</v>
+        <v>-3.758619</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>11.299626</v>
+        <v>-11.106352</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>15.256534</v>
+        <v>-14.9695</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>3.786045</v>
@@ -1870,13 +1870,13 @@
         </is>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.694438</v>
+        <v>-0.694438</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.585067</v>
+        <v>-0.585067</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.805903</v>
+        <v>-1.805903</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>-0.039686</v>
@@ -1963,22 +1963,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>10.51418710431099</v>
+        <v>189.485812895689</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -1986,13 +1986,13 @@
         </is>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>-0</v>
@@ -32691,13 +32691,13 @@
         </is>
       </c>
       <c r="L321" s="5" t="n">
-        <v>0.694438</v>
+        <v>-0.694438</v>
       </c>
       <c r="M321" s="5" t="n">
-        <v>0.585067</v>
+        <v>-0.585067</v>
       </c>
       <c r="N321" s="5" t="n">
-        <v>1.805903</v>
+        <v>-1.805903</v>
       </c>
       <c r="O321" t="inlineStr">
         <is>
@@ -32932,10 +32932,10 @@
         </is>
       </c>
       <c r="L324" s="5" t="n">
-        <v>0.236159</v>
+        <v>-0.236159</v>
       </c>
       <c r="M324" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0438</v>
       </c>
       <c r="N324" t="inlineStr">
         <is>
@@ -33015,13 +33015,13 @@
         </is>
       </c>
       <c r="L325" s="5" t="n">
-        <v>0.930597</v>
+        <v>-0.930597</v>
       </c>
       <c r="M325" s="5" t="n">
-        <v>0.628867</v>
+        <v>-0.628867</v>
       </c>
       <c r="N325" s="5" t="n">
-        <v>1.805903</v>
+        <v>-1.805903</v>
       </c>
       <c r="O325" t="inlineStr">
         <is>
@@ -34217,10 +34217,10 @@
         </is>
       </c>
       <c r="I340" s="5" t="n">
-        <v>3.276234</v>
+        <v>-3.276234</v>
       </c>
       <c r="J340" s="5" t="n">
-        <v>1.040172</v>
+        <v>-1.040172</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
@@ -34462,10 +34462,10 @@
         </is>
       </c>
       <c r="I343" s="5" t="n">
-        <v>3.24054</v>
+        <v>-3.24054</v>
       </c>
       <c r="J343" s="5" t="n">
-        <v>1.041928</v>
+        <v>-1.041928</v>
       </c>
       <c r="K343" t="inlineStr">
         <is>
@@ -35086,13 +35086,13 @@
         </is>
       </c>
       <c r="G351" s="5" t="n">
-        <v>11.202989</v>
+        <v>-11.202989</v>
       </c>
       <c r="H351" s="5" t="n">
-        <v>15.113017</v>
+        <v>-15.113017</v>
       </c>
       <c r="I351" s="5" t="n">
-        <v>3.276234</v>
+        <v>-3.276234</v>
       </c>
       <c r="J351" t="inlineStr">
         <is>
@@ -36121,10 +36121,10 @@
         </is>
       </c>
       <c r="E364" s="5" t="n">
-        <v>1.904619</v>
+        <v>-1.904619</v>
       </c>
       <c r="F364" s="5" t="n">
-        <v>3.758619</v>
+        <v>-3.758619</v>
       </c>
       <c r="G364" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/XBOT.xlsx
+++ b/output/pdf_financials_xlsx/XBOT.xlsx
@@ -937,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000497</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000168</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001871</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -960,13 +960,13 @@
         <v>0</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.036978</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.023503</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.011211</v>
       </c>
       <c r="N12" s="3" t="n">
         <v>0</v>
@@ -1757,13 +1757,13 @@
         <v>-3.758619</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.202989</v>
+        <v>-11.202492</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-15.113017</v>
+        <v>-15.112849</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.661177</v>
+        <v>3.663048</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>1.040172</v>
@@ -1780,13 +1780,13 @@
         <v>-0.585067</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.805903</v>
+        <v>-1.768925</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.039686</v>
+        <v>-0.016183</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-21.698907</v>
+        <v>-21.710118</v>
       </c>
       <c r="N27" s="3" t="n">
         <v>-11.28116</v>
@@ -1853,13 +1853,13 @@
         <v>-3.758619</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.106352</v>
+        <v>-11.105855</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-14.9695</v>
+        <v>-14.969332</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.786045</v>
+        <v>3.787916</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>1.093894</v>
@@ -1876,13 +1876,13 @@
         <v>-0.585067</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.805903</v>
+        <v>-1.768925</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.039686</v>
+        <v>-0.016183</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-21.35664</v>
+        <v>-21.367851</v>
       </c>
       <c r="N29" s="3" t="n">
         <v>-10.758875</v>
@@ -1950,7 +1950,7 @@
         </is>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-2340.358801889677</v>
+        <v>-2341.587354814106</v>
       </c>
       <c r="N30" s="3" t="n">
         <v>-534.2632107412038</v>
@@ -2086,7 +2086,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.557118</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>11.614028</v>
@@ -2119,10 +2119,10 @@
         <v>2.427444</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.440933</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>5.191786</v>
       </c>
     </row>
     <row r="35">
@@ -2178,7 +2178,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.557118</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>11.614028</v>
@@ -2211,10 +2211,10 @@
         <v>2.427444</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.440933</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>5.191786</v>
       </c>
     </row>
     <row r="37">
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>8.741154999999999</v>
+        <v>8.184037</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.126585</v>
@@ -2763,10 +2763,10 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.542242</v>
+        <v>0.101309</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>5.437993</v>
+        <v>0.246207</v>
       </c>
     </row>
     <row r="49">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -14392,7 +14392,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
@@ -29440,7 +29440,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -29523,7 +29523,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -31682,7 +31682,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -34598,7 +34598,11 @@
           <t>General and administrative expenditures (Note 14) $</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -34833,7 +34837,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">

--- a/output/pdf_financials_xlsx/XBOT.xlsx
+++ b/output/pdf_financials_xlsx/XBOT.xlsx
@@ -5743,7 +5743,7 @@
         <v>0</v>
       </c>
       <c r="H112" s="3" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="I112" s="3" t="n">
         <v>0</v>
@@ -20899,7 +20899,11 @@
           <t>Proceeds on disposal of property &amp; equipment</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/XBOT.xlsx
+++ b/output/pdf_financials_xlsx/XBOT.xlsx
@@ -1129,10 +1129,10 @@
         <v>-3.758619</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-11.202989</v>
+        <v>-11.529339</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-15.113017</v>
+        <v>-15.357375</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>3.661177</v>
@@ -1177,13 +1177,13 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>0.32635</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>0.244358</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-6.937411</v>
+        <v>0.384943</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-2.080344</v>
@@ -1398,10 +1398,10 @@
         <v>-0.039686</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>-8.675371</v>
+        <v>-12.624536</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>-4.911382</v>
+        <v>-6.369778</v>
       </c>
     </row>
     <row r="21">
@@ -1446,10 +1446,10 @@
         <v>0</v>
       </c>
       <c r="M21" s="3" t="n">
-        <v>0</v>
+        <v>3.949165</v>
       </c>
       <c r="N21" s="3" t="n">
-        <v>0</v>
+        <v>1.458396</v>
       </c>
     </row>
     <row r="22">
@@ -1757,10 +1757,10 @@
         <v>-3.758619</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.202492</v>
+        <v>-11.528842</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-15.112849</v>
+        <v>-15.357207</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>3.663048</v>
@@ -1853,10 +1853,10 @@
         <v>-3.758619</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.105855</v>
+        <v>-11.432205</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-14.969332</v>
+        <v>-15.21369</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>3.787916</v>
@@ -1969,13 +1969,13 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-2.830604599274945</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.591144319911443</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>189.485812895689</v>
+        <v>10.51418710431099</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>200</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>0.408207</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>0.134149</v>
       </c>
     </row>
     <row r="65">
@@ -3683,10 +3683,10 @@
         <v>0</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.310963</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.173766</v>
       </c>
     </row>
     <row r="68">
@@ -3821,10 +3821,10 @@
         <v>0</v>
       </c>
       <c r="M70" s="3" t="n">
-        <v>0</v>
+        <v>0.226754</v>
       </c>
       <c r="N70" s="3" t="n">
-        <v>0</v>
+        <v>0.200828</v>
       </c>
     </row>
     <row r="71">
@@ -3867,10 +3867,10 @@
         <v>0</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>1.789336</v>
+        <v>2.01609</v>
       </c>
       <c r="N71" s="3" t="n">
-        <v>1.42243</v>
+        <v>1.623258</v>
       </c>
     </row>
     <row r="72">
@@ -4054,7 +4054,7 @@
         <v>0</v>
       </c>
       <c r="N75" s="3" t="n">
-        <v>0.420253</v>
+        <v>0.219425</v>
       </c>
     </row>
     <row r="76">
@@ -4311,10 +4311,10 @@
         </is>
       </c>
       <c r="M80" s="3" t="n">
-        <v>0.2513252073837361</v>
+        <v>0.2796318343381853</v>
       </c>
       <c r="N80" s="3" t="n">
-        <v>0.3882996089787477</v>
+        <v>0.4431222954181394</v>
       </c>
     </row>
     <row r="81">
@@ -5160,10 +5160,10 @@
         <v>-0.039686</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>-8.675371</v>
+        <v>-12.624536</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>-4.911382</v>
+        <v>-6.369778</v>
       </c>
     </row>
     <row r="100">
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.181038</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.263729</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>-0.213</v>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.181038</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.263729</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>-0.213</v>
@@ -8012,7 +8012,11 @@
           <t>Lease liabilities 10</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -16034,7 +16038,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -16838,7 +16846,11 @@
           <t>Deferred income tax recovery 19</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
@@ -22041,7 +22053,11 @@
           <t>Gain on completion of private placement</t>
         </is>
       </c>
-      <c r="D190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -26192,7 +26208,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E241" s="5" t="n">
         <v>-0.181038</v>
       </c>
@@ -29936,7 +29956,11 @@
           <t>Deferred income tax recovery 19</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -30017,7 +30041,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D288" t="inlineStr"/>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E288" t="inlineStr">
         <is>
           <t>-</t>
@@ -30096,7 +30124,11 @@
           <t>Net income from discontinued operations 20</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -34114,7 +34146,11 @@
           <t>Deferred income tax recovery (note 12)</t>
         </is>
       </c>
-      <c r="D339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E339" t="inlineStr">
         <is>
           <t>-</t>
@@ -35001,7 +35037,11 @@
           <t>Deferred income tax recovery (Note 12)</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E350" t="inlineStr">
         <is>
           <t>-</t>
